--- a/docs/materials/parts-table.xlsx
+++ b/docs/materials/parts-table.xlsx
@@ -82637,7 +82637,7 @@
       </c>
       <c r="C2156" s="4" t="inlineStr">
         <is>
-          <t>口 止 聶</t>
+          <t>足 聶</t>
         </is>
       </c>
       <c r="D2156" s="4" t="inlineStr">
@@ -82649,12 +82649,12 @@
       <c r="F2156" s="5" t="n"/>
       <c r="G2156" s="4" t="inlineStr">
         <is>
-          <t>口 止 聶 耳 聑</t>
+          <t>足 口 龰 聶 耳 聑</t>
         </is>
       </c>
       <c r="H2156" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2156" s="3" t="n"/>

--- a/docs/materials/parts-table.xlsx
+++ b/docs/materials/parts-table.xlsx
@@ -3189,7 +3189,7 @@
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>虫 莫 艹 十 旲 日 大 一 人</t>
+          <t>虫 莫 艹 十 日 大 一 人</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -16119,7 +16119,7 @@
       <c r="F411" s="5" t="inlineStr"/>
       <c r="G411" s="4" t="inlineStr">
         <is>
-          <t>木 莫 艹 十 旲 日 大 一 人</t>
+          <t>木 莫 艹 十 日 大 一 人</t>
         </is>
       </c>
       <c r="H411" s="4" t="inlineStr">
@@ -29837,7 +29837,7 @@
       <c r="F772" s="5" t="inlineStr"/>
       <c r="G772" s="4" t="inlineStr">
         <is>
-          <t>莫 艹 十 旲 日 大 一 人 小 丶</t>
+          <t>莫 艹 十 日 大 一 人 小 丶</t>
         </is>
       </c>
       <c r="H772" s="4" t="inlineStr">
@@ -44335,7 +44335,7 @@
       <c r="F1151" s="5" t="n"/>
       <c r="G1151" s="4" t="inlineStr">
         <is>
-          <t>莫 艹 十 旲 日 大 一 人 力 丿 𠃌</t>
+          <t>莫 艹 十 日 大 一 人 力 丿 𠃌</t>
         </is>
       </c>
       <c r="H1151" s="4" t="inlineStr">
@@ -50109,7 +50109,7 @@
       <c r="F1302" s="5" t="n"/>
       <c r="G1302" s="4" t="inlineStr">
         <is>
-          <t>莫 艹 十 旲 日 大 一 人</t>
+          <t>莫 艹 十 日 大 一 人</t>
         </is>
       </c>
       <c r="H1302" s="4" t="inlineStr">
@@ -53339,7 +53339,7 @@
       <c r="F1387" s="5" t="n"/>
       <c r="G1387" s="4" t="inlineStr">
         <is>
-          <t>莫 艹 十 旲 日 大 一 人 巾</t>
+          <t>莫 艹 十 日 大 一 人 巾</t>
         </is>
       </c>
       <c r="H1387" s="4" t="inlineStr">
@@ -68157,7 +68157,7 @@
       <c r="F1776" s="5" t="n"/>
       <c r="G1776" s="4" t="inlineStr">
         <is>
-          <t>宀 莫 艹 十 旲 日 大 一 人</t>
+          <t>宀 莫 艹 十 日 大 一 人</t>
         </is>
       </c>
       <c r="H1776" s="4" t="inlineStr">
@@ -70905,7 +70905,7 @@
       <c r="F1848" s="5" t="n"/>
       <c r="G1848" s="4" t="inlineStr">
         <is>
-          <t>弓 玄 亠 丶 一 幺</t>
+          <t>弓 玄</t>
         </is>
       </c>
       <c r="H1848" s="4" t="inlineStr">
@@ -75215,7 +75215,7 @@
       <c r="F1961" s="5" t="n"/>
       <c r="G1961" s="4" t="inlineStr">
         <is>
-          <t>玄 亠 丶 一 幺 丷 八 十</t>
+          <t>玄 丷 八 十</t>
         </is>
       </c>
       <c r="H1961" s="4" t="inlineStr">
@@ -75873,7 +75873,7 @@
       <c r="F1978" s="5" t="n"/>
       <c r="G1978" s="4" t="inlineStr">
         <is>
-          <t>目 玄 亠 丶 一 幺</t>
+          <t>目 玄</t>
         </is>
       </c>
       <c r="H1978" s="4" t="inlineStr">
@@ -77769,7 +77769,7 @@
       <c r="F2028" s="5" t="n"/>
       <c r="G2028" s="4" t="inlineStr">
         <is>
-          <t>火 八 人 玄 亠 丶 一 幺</t>
+          <t>火 八 人 玄</t>
         </is>
       </c>
       <c r="H2028" s="4" t="inlineStr">
@@ -81829,26 +81829,18 @@
           <t>南一6上第10課</t>
         </is>
       </c>
-      <c r="C2135" s="4" t="inlineStr">
-        <is>
-          <t>勹 厶</t>
-        </is>
-      </c>
+      <c r="C2135" s="4" t="n"/>
       <c r="D2135" s="4" t="inlineStr">
         <is>
-          <t>右上包圍</t>
+          <t>獨體字</t>
         </is>
       </c>
       <c r="E2135" s="5" t="n"/>
       <c r="F2135" s="5" t="n"/>
-      <c r="G2135" s="4" t="inlineStr">
-        <is>
-          <t>勹 厶</t>
-        </is>
-      </c>
+      <c r="G2135" s="4" t="n"/>
       <c r="H2135" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2135" s="3" t="n"/>
@@ -81945,7 +81937,7 @@
       </c>
       <c r="C2138" s="4" t="inlineStr">
         <is>
-          <t>金 羅</t>
+          <t>金 罒 糹 隹</t>
         </is>
       </c>
       <c r="D2138" s="4" t="inlineStr">
@@ -81957,12 +81949,12 @@
       <c r="F2138" s="5" t="n"/>
       <c r="G2138" s="4" t="inlineStr">
         <is>
-          <t>金 人 王 一 土 十 丷 羅 罒 維 糹 幺 丶 隹</t>
+          <t>金 人 王 一 土 十 丷 罒 糹 幺 丶 隹</t>
         </is>
       </c>
       <c r="H2138" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2138" s="3" t="n"/>
@@ -82059,7 +82051,7 @@
       </c>
       <c r="C2141" s="4" t="inlineStr">
         <is>
-          <t>艹 旲</t>
+          <t>艹 日 大</t>
         </is>
       </c>
       <c r="D2141" s="4" t="inlineStr">
@@ -82071,12 +82063,12 @@
       <c r="F2141" s="5" t="n"/>
       <c r="G2141" s="4" t="inlineStr">
         <is>
-          <t>艹 十 旲 日 大 一 人</t>
+          <t>艹 十 日 大 一 人</t>
         </is>
       </c>
       <c r="H2141" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2141" s="3" t="n"/>
@@ -82137,26 +82129,18 @@
           <t>南一6上第11課</t>
         </is>
       </c>
-      <c r="C2143" s="4" t="inlineStr">
-        <is>
-          <t>亠 幺</t>
-        </is>
-      </c>
+      <c r="C2143" s="4" t="n"/>
       <c r="D2143" s="4" t="inlineStr">
         <is>
-          <t>上下</t>
+          <t>獨體字</t>
         </is>
       </c>
       <c r="E2143" s="5" t="n"/>
       <c r="F2143" s="5" t="n"/>
-      <c r="G2143" s="4" t="inlineStr">
-        <is>
-          <t>亠 丶 一 幺</t>
-        </is>
-      </c>
+      <c r="G2143" s="4" t="n"/>
       <c r="H2143" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2143" s="3" t="n"/>
@@ -82253,7 +82237,7 @@
       </c>
       <c r="C2146" s="4" t="inlineStr">
         <is>
-          <t>旉 攵</t>
+          <t>甫 方 攵</t>
         </is>
       </c>
       <c r="D2146" s="4" t="inlineStr">
@@ -82265,12 +82249,12 @@
       <c r="F2146" s="5" t="n"/>
       <c r="G2146" s="4" t="inlineStr">
         <is>
-          <t>旉 甫 十 月 丶 方 亠 一 丿 𠃌 攵</t>
+          <t>甫 十 月 丶 方 亠 一 丿 𠃌 攵</t>
         </is>
       </c>
       <c r="H2146" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2146" s="3" t="n"/>
@@ -82333,7 +82317,7 @@
       </c>
       <c r="C2148" s="4" t="inlineStr">
         <is>
-          <t>扌 鼻</t>
+          <t>扌 自 田 丌</t>
         </is>
       </c>
       <c r="D2148" s="4" t="inlineStr">
@@ -82345,12 +82329,12 @@
       <c r="F2148" s="5" t="n"/>
       <c r="G2148" s="4" t="inlineStr">
         <is>
-          <t>扌 鼻 自 畀 田 丌 一 丿 丨</t>
+          <t>扌 自 田 丌 一 丿 丨</t>
         </is>
       </c>
       <c r="H2148" s="4" t="inlineStr">
         <is>
-          <t>自動（parts.js）</t>
+          <t>人工（lessons.js）</t>
         </is>
       </c>
       <c r="I2148" s="3" t="n"/>
